--- a/WorkBot/main/data/order_archive/US Foods/US Foods_Triphammer_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/US Foods/US Foods_Triphammer_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,6 +668,468 @@
         <v>104.62</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4455234</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Artichoke Hrt Qtrd</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="E15" t="n">
+        <v>45.87</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3791747</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Can - Roasted Red Pepper (Strips)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="E16" t="n">
+        <v>101.98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8457368</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Oil - Corn</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="E17" t="n">
+        <v>95.98</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1030192</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BBQ - Sauce</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>64.98999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7520950</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Can - Pizza Sauce</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="E19" t="n">
+        <v>42.35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>9227984</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pasta - Farfalle (Bowtie)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="E20" t="n">
+        <v>24.88</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0490508</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Brie</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="E21" t="n">
+        <v>109.76</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1027629</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cheddar - (Sliced)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="E22" t="n">
+        <v>381.96</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6432884</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pepper Jack (Sliced)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>199.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1028165</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pickle - Dill Chip</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>9546982</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Arugula - Fresh</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="E25" t="n">
+        <v>48.66</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2006567</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Potato - Chef</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="E26" t="n">
+        <v>21.45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2739175</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sour Cream</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="E27" t="n">
+        <v>25.84</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>9047468</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Egg Patty</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="E28" t="n">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1025719</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Green Bean - FRZ Whole</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>32.05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3991049</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sausage - Italian Sweet</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>68.83</v>
+      </c>
+      <c r="E30" t="n">
+        <v>68.83</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1365278</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vegan Chicken Tenders</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>88.98999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4254710</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Veggie Burger</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="E32" t="n">
+        <v>52.21</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>9970237</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Chicken Filet - Breaded 4 oz (Raw)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>169.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2825368</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sausage - Chicken Patty</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="E34" t="n">
+        <v>407.92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4157160</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Spanakopita</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>72.98999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7529232</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Wrap - Wheat (10")</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="E36" t="n">
+        <v>31.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
